--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487803_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487803_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4884</v>
+        <v>3.729</v>
       </c>
       <c r="E2" t="n">
-        <v>4.313</v>
+        <v>3.1995</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1754</v>
+        <v>0.5295</v>
       </c>
       <c r="G2" t="n">
         <v>1.348</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>3.356</v>
+        <v>1.5966</v>
       </c>
       <c r="T2" t="n">
-        <v>1.826</v>
+        <v>0.7125</v>
       </c>
       <c r="U2" t="n">
-        <v>1.53</v>
+        <v>0.8841</v>
       </c>
       <c r="V2" t="n">
         <v>1.6168</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8995</v>
+        <v>3.5313</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2373</v>
+        <v>6.5169</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3379</v>
+        <v>-2.9856</v>
       </c>
       <c r="G3" t="n">
         <v>4.691</v>
@@ -688,13 +688,13 @@
         <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0046</v>
+        <v>0.6272</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1891</v>
+        <v>0.4687</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1937</v>
+        <v>0.1586</v>
       </c>
       <c r="V3" t="n">
         <v>-3.0356</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4786</v>
+        <v>1.859</v>
       </c>
       <c r="E4" t="n">
-        <v>4.03</v>
+        <v>3.4104</v>
       </c>
       <c r="F4" t="n">
         <v>-1.5514</v>
@@ -766,10 +766,10 @@
         <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>1.233</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5155</v>
+        <v>0.8959</v>
       </c>
       <c r="U4" t="n">
         <v>-0.2824</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8858</v>
+        <v>1.0964</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7023</v>
+        <v>-0.3156</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5881</v>
+        <v>1.412</v>
       </c>
       <c r="G5" t="n">
         <v>-0.579</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7679</v>
+        <v>0.9784</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0562</v>
+        <v>0.3306</v>
       </c>
       <c r="U5" t="n">
-        <v>0.824</v>
+        <v>0.6479</v>
       </c>
       <c r="V5" t="n">
         <v>0.697</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8648</v>
+        <v>1.054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9402</v>
+        <v>1.0707</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="G6" t="n">
         <v>1.2947</v>
@@ -922,13 +922,13 @@
         <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8462</v>
+        <v>-0.657</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3138</v>
+        <v>-0.1833</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5324</v>
+        <v>-0.4736</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5513</v>
+        <v>0.7722</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0169</v>
+        <v>0.2964</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5344</v>
+        <v>0.4757</v>
       </c>
       <c r="G7" t="n">
         <v>1.2491</v>
@@ -1000,13 +1000,13 @@
         <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0515</v>
+        <v>0.1693</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1957</v>
+        <v>0.0838</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1442</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4002</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7877</v>
+        <v>0.9601</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3876</v>
+        <v>-0.2701</v>
       </c>
       <c r="G8" t="n">
         <v>0.2566</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6889</v>
+        <v>-0.3991</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0248</v>
+        <v>0.1972</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7137</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3198</v>
+        <v>-0.3664</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3992</v>
+        <v>0.2019</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9206</v>
+        <v>-0.5683</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5172</v>
@@ -1156,13 +1156,13 @@
         <v>2.4974</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3868</v>
+        <v>1.3402</v>
       </c>
       <c r="T9" t="n">
-        <v>0.332</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0548</v>
+        <v>0.4071</v>
       </c>
       <c r="V9" t="n">
         <v>0.3538</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9529</v>
+        <v>-1.255</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7273</v>
+        <v>-0.912</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2256</v>
+        <v>-0.343</v>
       </c>
       <c r="G10" t="n">
         <v>0.8242</v>
@@ -1234,13 +1234,13 @@
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1807</v>
+        <v>0.5172</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6524</v>
+        <v>0.1629</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4717</v>
+        <v>0.3543</v>
       </c>
       <c r="V10" t="n">
         <v>-3.637</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2493</v>
+        <v>-3.3815</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0339</v>
+        <v>-1.2249</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2153</v>
+        <v>-2.1566</v>
       </c>
       <c r="G11" t="n">
         <v>-3.86</v>
@@ -1312,13 +1312,13 @@
         <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5702</v>
+        <v>0.4379</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9192</v>
+        <v>0.7282</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.349</v>
+        <v>-0.2903</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5838</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1714</v>
+        <v>-4.8751</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8912</v>
+        <v>-2.6535</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2803</v>
+        <v>-2.2216</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0001</v>
@@ -1390,13 +1390,13 @@
         <v>1.6649</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1318</v>
+        <v>0.1646</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4005</v>
+        <v>0.6382</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5324</v>
+        <v>-0.4736</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5827</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8752</v>
+        <v>2.853900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>9.571200000000003</v>
+        <v>10.5499</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.696199999999999</v>
+        <v>-7.696099999999999</v>
       </c>
       <c r="G13" t="n">
         <v>2.551400000000001</v>
@@ -1468,13 +1468,13 @@
         <v>18.7306</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4102</v>
+        <v>5.3887</v>
       </c>
       <c r="T13" t="n">
-        <v>3.989</v>
+        <v>4.967700000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4211</v>
+        <v>0.4212999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>-8.2081</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.942</v>
+        <v>4.9268</v>
       </c>
       <c r="E14" t="n">
-        <v>6.7408</v>
+        <v>6.205</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7988</v>
+        <v>-1.2782</v>
       </c>
       <c r="G14" t="n">
         <v>2.611</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.884</v>
+        <v>-0.8992</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3196</v>
+        <v>-0.2162</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2036</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>4.0474</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8747</v>
+        <v>1.5431</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4604</v>
+        <v>2.1034</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5857</v>
+        <v>-0.5603</v>
       </c>
       <c r="G15" t="n">
         <v>4.3422</v>
@@ -1624,13 +1624,13 @@
         <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2832</v>
+        <v>-0.6149</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7829</v>
+        <v>-0.14</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5003</v>
+        <v>-0.4749</v>
       </c>
       <c r="V15" t="n">
         <v>0.9376</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0911</v>
+        <v>1.0105</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5138</v>
+        <v>2.4643</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4226</v>
+        <v>-1.4538</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5122</v>
+        <v>0.8054</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1342</v>
+        <v>1.0471</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.378</v>
+        <v>-0.2417</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5649</v>
+        <v>3.3081</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9298999999999999</v>
+        <v>2.4517</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3649</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9473</v>
+        <v>-2.5027</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2043</v>
+        <v>-1.4046</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7429</v>
+        <v>-1.0981</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8731</v>
+        <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-1.4459</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9134</v>
+        <v>-0.62</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1195</v>
+        <v>-0.8259</v>
       </c>
       <c r="V16" t="n">
-        <v>3.4637</v>
+        <v>1.2347</v>
       </c>
       <c r="W16" t="n">
-        <v>4.0863</v>
+        <v>1.8574</v>
       </c>
       <c r="X16" t="n">
         <v>-0.6227</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3522</v>
+        <v>-0.2399</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7142</v>
+        <v>-1.2502</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0664</v>
+        <v>1.0103</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8054</v>
+        <v>-4.0378</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0471</v>
+        <v>-2.885</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2417</v>
+        <v>-1.1528</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3081</v>
+        <v>-1.7434</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4517</v>
+        <v>-1.7254</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.018</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5027</v>
+        <v>-2.2944</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4046</v>
+        <v>-1.1596</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0981</v>
+        <v>-1.1348</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4974</v>
+        <v>2.9137</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.8086</v>
+        <v>-0.198</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3701</v>
+        <v>0.3663</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4385</v>
+        <v>-0.5643</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2347</v>
+        <v>2.1228</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8574</v>
+        <v>1.1675</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6227</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.374</v>
+        <v>-0.4533</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0358</v>
+        <v>-0.7914</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6619</v>
+        <v>0.3382</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.0378</v>
+        <v>-1.1398</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.885</v>
+        <v>-0.2131</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1528</v>
+        <v>-0.9266</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7434</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.7254</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.018</v>
+        <v>-0.7144</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2944</v>
+        <v>-0.5022</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1596</v>
+        <v>-0.2899</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1348</v>
+        <v>-0.2123</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9137</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3321</v>
+        <v>-0.146</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5806</v>
+        <v>-0.1538</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9127</v>
+        <v>0.0078</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1228</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.9553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5017</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8986</v>
+        <v>-0.4066</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3969</v>
+        <v>-0.1352</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1398</v>
+        <v>-1.5122</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2131</v>
+        <v>-1.1342</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9266</v>
+        <v>-0.378</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.5649</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07679999999999999</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7144</v>
+        <v>0.3649</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5022</v>
+        <v>-0.9473</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2899</v>
+        <v>-0.2043</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2123</v>
+        <v>-0.7429</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8325</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1944</v>
+        <v>-1.2446</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.261</v>
+        <v>-0.8062</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.4383</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.4637</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.0863</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6227</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6479</v>
+        <v>-0.9067</v>
       </c>
       <c r="E20" t="n">
-        <v>0.514</v>
+        <v>-0.2361</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1619</v>
+        <v>-0.6706</v>
       </c>
       <c r="G20" t="n">
         <v>-2.7978</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2519</v>
+        <v>0.9931</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5559</v>
+        <v>0.8058</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.304</v>
+        <v>0.1873</v>
       </c>
       <c r="V20" t="n">
         <v>0.6899</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.147</v>
+        <v>-2.0526</v>
       </c>
       <c r="E21" t="n">
-        <v>1.198</v>
+        <v>1.0908</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.345</v>
+        <v>-3.1434</v>
       </c>
       <c r="G21" t="n">
         <v>0.6379</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.079</v>
+        <v>0.0155</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3882</v>
+        <v>0.281</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4671</v>
+        <v>-0.2655</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4978</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5779</v>
+        <v>-3.7326</v>
       </c>
       <c r="E22" t="n">
         <v>-1.4831</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0948</v>
+        <v>-2.2494</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4603</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7131</v>
+        <v>0.5585</v>
       </c>
       <c r="T22" t="n">
         <v>0.0619</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6512</v>
+        <v>0.4965</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7902</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8751</v>
+        <v>-0.4464999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>7.696099999999999</v>
+        <v>7.696100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.571200000000001</v>
+        <v>-8.1424</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5514</v>
+        <v>-2.551399999999998</v>
       </c>
       <c r="H23" t="n">
         <v>1.1838</v>
@@ -2227,19 +2227,19 @@
         <v>10.6158</v>
       </c>
       <c r="L23" t="n">
-        <v>3.530800000000001</v>
+        <v>3.5308</v>
       </c>
       <c r="M23" t="n">
         <v>-16.6982</v>
       </c>
       <c r="N23" t="n">
-        <v>-9.431900000000001</v>
+        <v>-9.431899999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-7.2661</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.121799999999999</v>
+        <v>-3.1218</v>
       </c>
       <c r="Q23" t="n">
         <v>-18.7307</v>
@@ -2248,13 +2248,13 @@
         <v>15.609</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.410200000000001</v>
+        <v>-2.9815</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4212000000000003</v>
+        <v>-0.4212</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.9889</v>
+        <v>-2.5603</v>
       </c>
       <c r="V23" t="n">
         <v>8.208099999999998</v>
